--- a/data/trans_bre/IP22_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 2,64</t>
+          <t>-15,48; 2,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 9,75</t>
+          <t>-9,84; 10,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 9,88</t>
+          <t>-8,5; 11,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 13,83</t>
+          <t>-2,88; 14,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,73; 14,88</t>
+          <t>-57,38; 12,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,43; 51,99</t>
+          <t>-33,7; 54,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 66,43</t>
+          <t>-36,06; 81,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 123,4</t>
+          <t>-16,12; 130,39</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 11,3</t>
+          <t>-10,27; 10,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 6,68</t>
+          <t>-14,02; 7,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 9,95</t>
+          <t>-6,74; 10,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 5,16</t>
+          <t>-11,16; 5,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,73; 59,48</t>
+          <t>-34,49; 54,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 27,25</t>
+          <t>-41,66; 32,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,65; 84,89</t>
+          <t>-34,21; 85,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,06; 55,43</t>
+          <t>-58,37; 63,32</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 12,3</t>
+          <t>-10,4; 11,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 7,26</t>
+          <t>-13,67; 6,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 3,33</t>
+          <t>-15,76; 5,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 4,85</t>
+          <t>-22,7; 4,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 65,34</t>
+          <t>-38,14; 58,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,09; 42,5</t>
+          <t>-48,12; 39,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-65,32; 28,05</t>
+          <t>-63,38; 45,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-70,64; 36,49</t>
+          <t>-72,71; 37,68</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 5,94</t>
+          <t>-8,31; 4,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 6,18</t>
+          <t>-7,69; 6,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 8,59</t>
+          <t>-2,92; 9,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 9,42</t>
+          <t>-7,6; 10,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 31,74</t>
+          <t>-31,62; 25,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,01; 25,15</t>
+          <t>-23,54; 22,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 62,49</t>
+          <t>-13,42; 73,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 71,5</t>
+          <t>-39,32; 74,29</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 2,55</t>
+          <t>-12,63; 2,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,74; -1,99</t>
+          <t>-18,12; -0,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 8,61</t>
+          <t>-6,7; 9,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 9,1</t>
+          <t>-6,5; 9,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-54,37; 17,03</t>
+          <t>-54,14; 19,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-53,57; -7,26</t>
+          <t>-51,51; -0,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 61,32</t>
+          <t>-29,96; 68,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 85,19</t>
+          <t>-35,2; 83,56</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 13,91</t>
+          <t>-7,53; 14,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 3,75</t>
+          <t>-21,26; 1,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 5,45</t>
+          <t>-12,46; 6,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 9,56</t>
+          <t>-6,8; 9,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,87; 110,12</t>
+          <t>-33,46; 112,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,46; 24,19</t>
+          <t>-73,87; 11,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-73,21; 66,36</t>
+          <t>-71,21; 88,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,95; 235,13</t>
+          <t>-62,22; 200,01</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 1,18</t>
+          <t>-6,01; 1,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 0,02</t>
+          <t>-7,77; -0,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 3,83</t>
+          <t>-2,6; 4,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 4,22</t>
+          <t>-3,8; 4,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 5,77</t>
+          <t>-24,94; 6,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 0,11</t>
+          <t>-26,68; -0,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 24,81</t>
+          <t>-13,67; 27,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 30,2</t>
+          <t>-22,07; 31,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP22_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>5,72</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 2,01</t>
+          <t>-15,65; 1,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 10,56</t>
+          <t>-9,91; 10,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 11,22</t>
+          <t>-8,31; 10,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 14,41</t>
+          <t>-2,35; 14,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,38; 12,71</t>
+          <t>-56,25; 12,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,7; 54,52</t>
+          <t>-34,14; 57,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-36,06; 81,8</t>
+          <t>-36,21; 77,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 130,39</t>
+          <t>-13,05; 129,18</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,08</t>
+          <t>-3,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-20,88%</t>
+          <t>-20,43%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 10,68</t>
+          <t>-8,47; 11,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 7,69</t>
+          <t>-14,45; 7,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 10,35</t>
+          <t>-7,19; 8,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 5,44</t>
+          <t>-11,94; 5,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 54,16</t>
+          <t>-30,85; 59,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,66; 32,97</t>
+          <t>-41,71; 32,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 85,21</t>
+          <t>-35,13; 78,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,37; 63,32</t>
+          <t>-60,84; 62,06</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-7,19</t>
+          <t>-7,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-32,88%</t>
+          <t>-34,7%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 11,21</t>
+          <t>-11,71; 9,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 6,93</t>
+          <t>-13,36; 7,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 5,74</t>
+          <t>-15,16; 4,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 4,53</t>
+          <t>-19,86; 4,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,14; 58,19</t>
+          <t>-41,5; 47,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 39,09</t>
+          <t>-47,55; 40,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-63,38; 45,13</t>
+          <t>-63,94; 34,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-72,71; 37,68</t>
+          <t>-66,5; 43,87</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 4,9</t>
+          <t>-8,1; 5,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 6,04</t>
+          <t>-8,43; 6,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 9,29</t>
+          <t>-2,74; 9,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 10,25</t>
+          <t>-6,15; 7,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 25,84</t>
+          <t>-31,6; 28,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 22,73</t>
+          <t>-25,59; 25,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 73,67</t>
+          <t>-14,58; 68,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 74,29</t>
+          <t>-32,61; 57,58</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 2,98</t>
+          <t>-12,55; 2,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,12; -0,14</t>
+          <t>-18,24; -1,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 9,04</t>
+          <t>-6,42; 8,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 9,21</t>
+          <t>-8,36; 9,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 19,07</t>
+          <t>-52,11; 16,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-51,51; -0,36</t>
+          <t>-52,9; -4,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,96; 68,16</t>
+          <t>-30,31; 63,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,2; 83,56</t>
+          <t>-42,49; 81,96</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 14,28</t>
+          <t>-7,42; 13,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 1,75</t>
+          <t>-20,39; 3,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 6,49</t>
+          <t>-12,36; 6,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 9,59</t>
+          <t>-7,78; 11,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,46; 112,33</t>
+          <t>-34,87; 116,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,87; 11,0</t>
+          <t>-73,46; 22,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,21; 88,7</t>
+          <t>-69,44; 83,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-62,22; 200,01</t>
+          <t>-62,48; 305,1</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 1,16</t>
+          <t>-5,55; 1,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,77; -0,21</t>
+          <t>-8,01; -0,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 4,18</t>
+          <t>-2,31; 4,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 4,35</t>
+          <t>-3,42; 3,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 6,14</t>
+          <t>-23,14; 7,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,68; -0,88</t>
+          <t>-26,61; -1,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 27,02</t>
+          <t>-12,46; 25,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 31,75</t>
+          <t>-20,08; 26,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP22_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han utilizado las urgencias en el último año</t>
+          <t>Menores que han utilizado  algún servicio de urgencias en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-6,57</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,72</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-29,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38,37%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-6.574880246229445</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.07503853882024902</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.7020019141873834</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5.724776384105115</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.293574935565483</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.003080593132736149</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.03674790890867829</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.3837023749446878</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-15,65; 1,65</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,91; 10,62</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-8,31; 10,77</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,35; 14,06</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-56,25; 12,74</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-34,14; 57,74</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-36,21; 77,55</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-13,05; 129,18</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-15.6506831774932</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.908159741938151</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-8.313293793190908</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.349448226288481</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5624936173382544</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3414448777052143</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.3621158657267408</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.1304955603783191</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.652252089166476</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.62113559410308</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.77263412827045</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>14.06295415942199</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1273809663200664</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.5773500148749481</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.7754521816236277</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.291789139389534</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-3,65</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-3,01</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-12,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-20,43%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,47; 11,48</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-14,45; 7,09</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-7,19; 8,99</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-11,94; 5,73</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-30,85; 59,72</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-41,71; 32,91</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-35,13; 78,23</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-60,84; 62,06</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.023808184006733</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-3.649046400714689</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.530629572854467</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-3.007520777133488</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.04220011358410534</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1276170906348823</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.09633867349181302</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2042782164257544</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,52</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-7,32</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,34%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-13,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-28,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-34,7%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.471004520184838</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-14.44576486497492</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-7.193405006882768</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-11.93926833266497</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3085338197132959</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4171194472018211</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3512527824427141</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6084215225653438</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-11,71; 9,22</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-13,36; 7,18</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-15,16; 4,38</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-19,86; 4,91</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-41,5; 47,08</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-47,55; 40,92</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-63,94; 34,05</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-66,5; 43,87</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>11.47892148133302</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.085824756782458</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>8.985052472509111</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.725745671822637</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.5972276188546715</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.3291081659099076</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.7822571126031612</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.620594595397748</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,57</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,08</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-6,99%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-3,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.5559657097782472</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-3.173552304202412</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-5.521064689221944</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-7.317292176893886</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.02338923499569461</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1373325286990482</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.2878851843313978</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.3470072355244844</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-8,1; 5,54</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-8,43; 6,25</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,74; 9,14</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-6,15; 7,65</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-31,6; 28,18</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-25,59; 25,08</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-14,58; 68,23</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-32,61; 57,58</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-11.70998106801231</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-13.36283944096208</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-15.16010378589369</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-19.86140008022939</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4150269881227409</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4754880392012712</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6393713693059752</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6650012340992116</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.221214491521845</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.182154990872433</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.383476099081247</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.910173276182442</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.4707711454722309</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.4092228418841981</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.3404588716112466</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.4386711625663582</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-5,31</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-9,9</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-26,1%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-32,42%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-12,55; 2,55</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-18,24; -1,05</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-6,42; 8,93</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-8,36; 9,0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-52,11; 16,43</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-52,9; -4,59</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-30,31; 63,25</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-42,49; 81,96</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-1.566591425531835</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.038214254972281</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>3.075705326759126</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.586121770733436</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.06993833823960148</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.03522519196029009</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.1859680583782926</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.03700980396246334</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2,99</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-9,74</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-3,55</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16,76%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-41,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-25,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>15,86%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-8.099766613692228</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-8.430615373425688</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.7354352559705</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-6.145971060609575</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3159930189533045</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2559250287753302</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1458337364079667</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.326110736811425</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-7,42; 13,91</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-20,39; 3,18</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-12,36; 6,76</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-7,78; 11,19</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-34,87; 116,13</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-73,46; 22,08</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-69,44; 83,91</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-62,48; 305,1</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.542909102716671</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.254145604676407</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.139453141896235</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7.646955953212259</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2818203014907393</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.250802832703135</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.6822846969473673</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.5758480926620883</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-2,04</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-4,06</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-9,28%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-14,75%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-5.310113487224347</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-9.896616971333556</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.071775865043811</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.6174299760924568</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2610116758156187</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.324194764017777</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.06000067518422917</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.04023219373998697</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-5,55; 1,52</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-8,01; -0,39</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,31; 4,03</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-3,42; 3,57</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-23,14; 7,66</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-26,61; -1,3</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-12,46; 25,65</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-20,08; 26,81</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-12.55266405552582</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-18.24279596800488</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6.424607411588227</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-8.360160455032837</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.5211225383784192</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.528973418373367</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3030998908589912</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.424933493855897</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.551523182810556</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-1.054487887991684</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>8.928993967052881</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>8.995926439745498</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.1643185700672386</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-0.04586534328425346</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.6325346582484727</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.8196191885428455</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2.988330002991602</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-9.735335146583143</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-3.549183775417417</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1.333998764570649</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.1675644064375762</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.4161784926875787</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.2564771711574462</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.1585623094706138</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-7.424656685158995</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-20.39047698123572</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-12.3550669616156</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-7.783869522522462</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.3487498132528598</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.7346476296978326</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.6943841003280757</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.6248363306712288</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>13.90962465367188</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3.180443405501954</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>6.757119105376562</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>11.18829260987645</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1.161296238268229</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.2208115497364125</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.8391108147183047</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>3.051043269491421</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-2.03861068575292</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-4.058842350772859</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.6745113345950016</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.2030091665588374</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.09280445857496482</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.1475156454260694</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.03948432469226803</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.01342744465648494</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-5.546279011364747</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-8.010363319266558</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.314895021666582</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-3.422809326620915</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.2314033169651968</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.2661231793321543</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.1246478914689766</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.2008346552713223</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.523109433375978</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-0.3918751567913713</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>4.030235623429226</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.572490361314004</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.07655452138680409</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>-0.01297204881091934</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.2565208154871507</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.2681303807663126</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
